--- a/mahsulotlar_50ta.xlsx
+++ b/mahsulotlar_50ta.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://sizning-rasm-havolangiz.com/rasm.jpg</t>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Klassik%20oq%20futbolka&amp;font=montserrat</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,11 @@
           <t>Nafas oluvchi mato, sport va faol dam olish uchun qulay.</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Sport%20futbolka%20%28nafas%20oluvchi%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -629,7 +633,11 @@
           <t>Yengil paxta aralashmasi, kundalik kiyish uchun.</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Chiziqli%20futbolka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -663,7 +671,11 @@
           <t>Zamonaviy print dizayni, yosh auditoriya uchun.</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Grafik%20futbolka%20%28print%20bilan%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -697,7 +709,11 @@
           <t>Yarim rasmiy uslub, yoqasi bilan klassik kroy.</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Po%D0%BB%D0%BE%20futbolka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -731,7 +747,11 @@
           <t>Erkin, keng fason, zamonaviy shahar uslubi.</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Oversize%20futbolka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -765,7 +785,11 @@
           <t>Bahor-kuz mavsumi uchun qulay, yengil trikotaj.</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Uzun%20yengli%20futbolka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -799,7 +823,11 @@
           <t>Nafis kesim, kundalik va sport uchun universal.</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=V-yoqali%20futbolka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -833,7 +861,11 @@
           <t>Yuqori sifatli paxta, zich to'qilgan mato.</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Premium%20paxta%20futbolka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -867,7 +899,11 @@
           <t>Ish uchun ideal, dazmollashni talab qilmaydigan mato.</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Rasmiy%20oq%20ko%27ylak&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -901,7 +937,11 @@
           <t>Yengil paxta mato, bahor-yoz kolleksiyasi.</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Chiziqli%20ko%27ylak&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -935,7 +975,11 @@
           <t>Yengil denim, kundalik uchun qulay tashqi qatlam.</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Denim%20ko%27ylak&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -969,7 +1013,11 @@
           <t>Ofis va rasmiy tadbirlar uchun mos kesim.</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Klassik%20ko%27k%20ko%27ylak&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1003,7 +1051,11 @@
           <t>Issiq mavsum uchun issiqlik saqlovchi mato.</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=F%D0%BB%D0%B0%D0%BD%D0%B5%D0%BB%D1%8C%20ko%27ylak&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1037,7 +1089,11 @@
           <t>Kundalik kiyish uchun yengil va qulay.</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Yengil%20zamonaviy%20ko%27ylak&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1071,7 +1127,11 @@
           <t>Zig'ir aralashmasi, yozgi issiq kunlar uchun.</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=L%D0%B8nen%20ko%27ylak&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1105,7 +1165,11 @@
           <t>Cho'ziluvchan mato, kundalik va yarim rasmiy uchun.</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Slim%20fit%20shim&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1139,7 +1203,11 @@
           <t>To'g'ri kroy, ofis uchun universal.</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Klassik%20to%27g%27ri%20shim&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1173,7 +1241,11 @@
           <t>Og'ir zichlikdagi denim, uzoq muddat xizmat qiladi.</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Denim%20jinsi%20shim&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1207,7 +1279,11 @@
           <t>Elastik bel qismi, sport va bo'sh vaqt uchun.</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Sport%20shim%20%28jogger%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1241,7 +1317,11 @@
           <t>Yarim rasmiy uslub, ko'p vaziyat uchun mos.</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Chino%20shim&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1275,7 +1355,11 @@
           <t>Ichki qatlami issiqlik saqlovchi, qish mavsumi uchun.</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Qish%20uchun%20issiq%20shim&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1309,7 +1393,11 @@
           <t>Ko'p cho'ntakli amaliy dizayn.</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Cargo%20shim%20%28kombinezon%20uslub%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1343,7 +1431,11 @@
           <t>Og'ir zichlikdagi denim, klassik kroy.</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Denim%20kurtka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1377,7 +1469,11 @@
           <t>Yengil, shamolga chidamli, kuz-qish mavsumi uchun.</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Zamonaviy%20bomber&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1411,7 +1507,11 @@
           <t>Issiq mavsum uchun, yengil va issiq to'ldiruvchi bilan.</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Qishki%20puxovik&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1445,7 +1545,11 @@
           <t>Zamonaviy uslub, eko-teridan tayyorlangan.</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=K%D0%BE%D0%B6%D0%B0%20kurtka%20%28%D1%8D%D0%BA%D0%BE%20teri%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1479,7 +1583,11 @@
           <t>Yengil, suv o'tkazmaydigan mato.</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Sport%20kurtka%20%28windbreaker%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1513,7 +1621,11 @@
           <t>Rasmiy uslub uchun uzun palto, yuqori sifat.</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Klassik%20palto&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1547,7 +1659,11 @@
           <t>Bahor-kuz mavsumi uchun yengil variant.</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Jinsi%20kurtka%20%28yengil%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1581,7 +1697,11 @@
           <t>Tabiiy teridan, metall pryajka bilan.</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Teri%20kamar&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1615,7 +1735,11 @@
           <t>Issiq mavsum uchun trikotaj shapka.</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Sport%20shapka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1649,7 +1773,11 @@
           <t>Rasmiy tadbirlar uchun ipak aralashmasi.</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Klassik%20galstuk&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1683,7 +1811,11 @@
           <t>UV himoyasi bilan zamonaviy dizayn.</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Quyosh%20ko%27zoynagi&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1717,7 +1849,11 @@
           <t>Kundalik va sport uchun keng sig'imli ryukzak.</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Sport%20sumka%20%28backpack%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1751,7 +1887,11 @@
           <t>Tabiiy teridan, ko'p bo'lim bilan.</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Charm%20hamyon&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1785,7 +1925,11 @@
           <t>Yumshoq trikotaj, qish uchun issiq.</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Sharf%20%28qishki%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1819,7 +1963,11 @@
           <t>Issiq mavsum uchun charm qo'lqop.</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Qo%27lqop%20%28charm%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1853,7 +2001,11 @@
           <t>Zamonaviy gradient dizayn, yozgi kolleksiya.</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Bosqichma-bosqich%20rangli%20futbolka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1887,7 +2039,11 @@
           <t>Zich to'qilgan rib mato, aniq siluet.</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Rib%20trikotaj%20futbolka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1921,7 +2077,11 @@
           <t>Sovuq mavsum uchun issiqlik saqlovchi ichki qatlam.</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Termofutbolka%20%28issiq%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1955,7 +2115,11 @@
           <t>Keng fason, zamonaviy shahar uslubi.</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Bejirim%20ko%27ylak%20%28oversize%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1989,7 +2153,11 @@
           <t>Retro uslub, noyob nақsh bilan.</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Vintage%20ko%27ylak&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2023,7 +2191,11 @@
           <t>Yozgi issiq kunlar uchun qisqa shim.</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Bermuda%20shim%20%28qisqa%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2057,7 +2229,11 @@
           <t>Rasmiy tadbirlar uchun kostyum bilan mos.</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Yengil%20kostyum%20shim&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2091,7 +2267,11 @@
           <t>Yumshoq, issiq, kundalik kiyish uchun qulay.</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Fleece%20kurtka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2125,7 +2305,11 @@
           <t>Yengillik va erkinlik uchun yengsiz variant.</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Yelek%20%28jilet%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2159,7 +2343,11 @@
           <t>Kundalik va sport uchun universal bosh kiyim.</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Sport%20kepka&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2193,7 +2381,11 @@
           <t>Nafis uslub uchun yengil aksessuar.</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Ipak%20ro%27mol&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2227,7 +2419,11 @@
           <t>Klassik dizayn, kundalik va rasmiy kiyimga mos.</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>https://placehold.co/600x600/14161f/f3f1ea?text=Soat%20%28klassik%29&amp;font=montserrat</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
